--- a/Plannings 2026 S39.xlsx
+++ b/Plannings 2026 S39.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A06EF1BD-7F7B-483F-A397-D5C858F621BE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6120,7 +6120,7 @@
       <c r="A46" s="20"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="39" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="2"/>
@@ -6132,7 +6132,7 @@
       <c r="A47" s="22"/>
       <c r="B47" s="24"/>
       <c r="C47" s="24"/>
-      <c r="D47" s="24" t="s">
+      <c r="D47" s="38" t="s">
         <v>75</v>
       </c>
       <c r="E47" s="24"/>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="45" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="18"/>
@@ -6288,7 +6288,7 @@
       <c r="A57" s="20"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="46" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="2"/>
@@ -6302,7 +6302,7 @@
       <c r="A58" s="20"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="D58" s="46"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="47" t="s">
@@ -6314,7 +6314,7 @@
       <c r="A59" s="22"/>
       <c r="B59" s="24"/>
       <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
+      <c r="D59" s="48"/>
       <c r="E59" s="24"/>
       <c r="F59" s="24"/>
       <c r="G59" s="48" t="s">
@@ -7543,13 +7543,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18701F86-DB93-445C-953C-8C414000BBB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86DDF764-0B5A-44B5-AB40-319194553184}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52AB36C8-F5FF-481C-A64F-24BA079B375D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35247376-8E7F-4853-B503-C64174BE633A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBA61D21-BDB7-44B7-A672-E6D0A824BB75}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2C474F2-04FB-4666-8D32-FACE7FBF4504}"/>
 </file>
--- a/Plannings 2026 S39.xlsx
+++ b/Plannings 2026 S39.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A06EF1BD-7F7B-483F-A397-D5C858F621BE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6120,7 +6120,7 @@
       <c r="A46" s="20"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="2"/>
@@ -6132,7 +6132,7 @@
       <c r="A47" s="22"/>
       <c r="B47" s="24"/>
       <c r="C47" s="24"/>
-      <c r="D47" s="38" t="s">
+      <c r="D47" s="24" t="s">
         <v>75</v>
       </c>
       <c r="E47" s="24"/>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
-      <c r="D56" s="45" t="s">
+      <c r="D56" s="18" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="18"/>
@@ -6288,7 +6288,7 @@
       <c r="A57" s="20"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="46" t="s">
+      <c r="D57" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="2"/>
@@ -6302,7 +6302,7 @@
       <c r="A58" s="20"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="46"/>
+      <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="47" t="s">
@@ -6314,7 +6314,7 @@
       <c r="A59" s="22"/>
       <c r="B59" s="24"/>
       <c r="C59" s="24"/>
-      <c r="D59" s="48"/>
+      <c r="D59" s="24"/>
       <c r="E59" s="24"/>
       <c r="F59" s="24"/>
       <c r="G59" s="48" t="s">
@@ -7543,13 +7543,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86DDF764-0B5A-44B5-AB40-319194553184}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18701F86-DB93-445C-953C-8C414000BBB7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35247376-8E7F-4853-B503-C64174BE633A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52AB36C8-F5FF-481C-A64F-24BA079B375D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2C474F2-04FB-4666-8D32-FACE7FBF4504}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBA61D21-BDB7-44B7-A672-E6D0A824BB75}"/>
 </file>
--- a/Plannings 2026 S39.xlsx
+++ b/Plannings 2026 S39.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A06EF1BD-7F7B-483F-A397-D5C858F621BE}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0320468-921D-4999-A3E8-1A9C3304F7BD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="133">
   <si>
     <t>Planning des salariés du 21/09/2026 au 27/09/2026</t>
   </si>
@@ -276,9 +276,6 @@
     <t>16:30/21:00</t>
   </si>
   <si>
-    <t>16:15/22:30</t>
-  </si>
-  <si>
     <t>FREIXEDAS-BERENGUER Maxime</t>
   </si>
   <si>
@@ -418,6 +415,12 @@
   </si>
   <si>
     <t>Commercial : stage Toussaint</t>
+  </si>
+  <si>
+    <t>16:15/17:15</t>
+  </si>
+  <si>
+    <t>17:15/22:30</t>
   </si>
 </sst>
 </file>
@@ -3858,1181 +3861,1269 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15D70C1D-ADF2-45B5-9817-EC3C6BF46F69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9144000" y="9878786"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>55</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>55</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC315DF8-42A1-4347-BF66-0B618EA71D09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9144000" y="10259786"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5414,10 +5505,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="45.7109375" customWidth="1"/>
+    <col min="1" max="8" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5444,7 +5535,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C3" s="57"/>
       <c r="D3" s="57"/>
@@ -6247,227 +6338,223 @@
       <c r="D54" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="E54" s="47" t="s">
+      <c r="E54" s="43" t="s">
         <v>46</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="37"/>
       <c r="H54" s="21"/>
     </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="22"/>
-      <c r="B55" s="48"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="48" t="s">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="33"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="E55" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="F55" s="24"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="25"/>
+      <c r="E55" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="37"/>
+      <c r="H55" s="21"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="33"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="21"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="22"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="F57" s="24"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="25"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="19"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="20"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" s="21"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="20"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="21"/>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="22"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="48"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="45" t="s">
+      <c r="H61" s="25"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" s="30"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="31"/>
+      <c r="E62" s="31"/>
+      <c r="F62" s="31"/>
+      <c r="G62" s="31"/>
+      <c r="H62" s="32"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="22"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" s="30"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31"/>
+      <c r="H65" s="32"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E66" s="18"/>
+      <c r="F66" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="H56" s="19"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="20"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" s="21"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="20"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="H58" s="21"/>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="22"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="H59" s="25"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B60" s="30"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="32"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="19" t="s">
+      <c r="G66" s="18"/>
+      <c r="H66" s="19"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="33"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="G67" s="2"/>
+      <c r="H67" s="21"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" s="30"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="31"/>
+      <c r="E68" s="31"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="32"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="30"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="32"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="H70" s="19" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="22"/>
-      <c r="B62" s="24"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B63" s="30"/>
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="31"/>
-      <c r="H63" s="32"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="E64" s="18"/>
-      <c r="F64" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="G64" s="18"/>
-      <c r="H64" s="19"/>
-    </row>
-    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="G65" s="2"/>
-      <c r="H65" s="21"/>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="B66" s="30"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="32"/>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="32"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="H68" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="20"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="H69" s="21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="20"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H70" s="53" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -6477,11 +6564,11 @@
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
-      <c r="G71" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H71" s="54" t="s">
-        <v>55</v>
+      <c r="G71" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="H71" s="21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -6491,9 +6578,11 @@
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="34" t="s">
+      <c r="G72" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="H72" s="53" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -6503,9 +6592,11 @@
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="21" t="s">
-        <v>100</v>
+      <c r="G73" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H73" s="54" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -6516,266 +6607,290 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="H74" s="53" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="33"/>
+      <c r="H74" s="34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="20"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
-      <c r="H75" s="54" t="s">
-        <v>87</v>
+      <c r="H75" s="21" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="G76" s="18"/>
-      <c r="H76" s="19"/>
+      <c r="A76" s="20"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="53" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="22"/>
-      <c r="B77" s="24"/>
-      <c r="C77" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="D77" s="24"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="G77" s="24"/>
-      <c r="H77" s="25"/>
+      <c r="A77" s="33"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="54" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B78" s="18"/>
+      <c r="C78" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" s="18"/>
+      <c r="H78" s="19"/>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="22"/>
+      <c r="B79" s="24"/>
+      <c r="C79" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="D79" s="24"/>
+      <c r="E79" s="24"/>
+      <c r="F79" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="G79" s="24"/>
+      <c r="H79" s="25"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B80" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="B78" s="36" t="s">
+      <c r="C80" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="C78" s="18" t="s">
+      <c r="H80" s="19"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="20"/>
+      <c r="B81" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G81" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="H81" s="21"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="20"/>
+      <c r="B82" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D78" s="18" t="s">
+      <c r="C82" s="2"/>
+      <c r="D82" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E78" s="18"/>
-      <c r="F78" s="18" t="s">
+      <c r="H82" s="21"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="22"/>
+      <c r="B83" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C83" s="24"/>
+      <c r="D83" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E83" s="24"/>
+      <c r="F83" s="24"/>
+      <c r="G83" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="H83" s="25"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="H84" s="19"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="20"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="H85" s="21"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="20"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="37"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="H86" s="21"/>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="22"/>
+      <c r="B87" s="24"/>
+      <c r="C87" s="24"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="24"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="H87" s="25"/>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B88" s="30"/>
+      <c r="C88" s="31"/>
+      <c r="D88" s="31"/>
+      <c r="E88" s="31"/>
+      <c r="F88" s="31"/>
+      <c r="G88" s="31"/>
+      <c r="H88" s="32"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G78" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="H78" s="19"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="20"/>
-      <c r="B79" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G79" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="H79" s="21"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="20"/>
-      <c r="B80" s="3" t="s">
+      <c r="F89" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C80" s="2"/>
-      <c r="D80" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H80" s="21"/>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="22"/>
-      <c r="B81" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="C81" s="24"/>
-      <c r="D81" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E81" s="24"/>
-      <c r="F81" s="24"/>
-      <c r="G81" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="H81" s="25"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B82" s="18"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="E82" s="18"/>
-      <c r="F82" s="18"/>
-      <c r="G82" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="H82" s="19"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="20"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="H83" s="21"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="20"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="37"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="H84" s="21"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="22"/>
-      <c r="B85" s="24"/>
-      <c r="C85" s="24"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="24"/>
-      <c r="F85" s="24"/>
-      <c r="G85" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="H85" s="25"/>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="B86" s="30"/>
-      <c r="C86" s="31"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="31"/>
-      <c r="H86" s="32"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="17" t="s">
+      <c r="G89" s="18"/>
+      <c r="H89" s="19"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="22"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="24"/>
+      <c r="D90" s="24"/>
+      <c r="E90" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F87" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" s="18"/>
-      <c r="H87" s="19"/>
-    </row>
-    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="22"/>
-      <c r="B88" s="24"/>
-      <c r="C88" s="24"/>
-      <c r="D88" s="24"/>
-      <c r="E88" s="24" t="s">
+      <c r="F90" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="G90" s="24"/>
+      <c r="H90" s="25"/>
+    </row>
+    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="F88" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="G88" s="24"/>
-      <c r="H88" s="25"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B89" s="30"/>
-      <c r="C89" s="31"/>
-      <c r="D89" s="31"/>
-      <c r="E89" s="31"/>
-      <c r="F89" s="31"/>
-      <c r="G89" s="31"/>
-      <c r="H89" s="32"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B90" s="35"/>
-      <c r="C90" s="35"/>
-      <c r="D90" s="35"/>
-      <c r="E90" s="35"/>
-      <c r="F90" s="35"/>
-      <c r="G90" s="35"/>
-      <c r="H90" s="35"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="31"/>
+      <c r="D91" s="31"/>
+      <c r="E91" s="31"/>
+      <c r="F91" s="31"/>
+      <c r="G91" s="31"/>
+      <c r="H91" s="32"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B92" s="35"/>
+      <c r="C92" s="35"/>
+      <c r="D92" s="35"/>
+      <c r="E92" s="35"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="35"/>
+      <c r="H92" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B63:H63"/>
-    <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B89:H89"/>
-    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B91:H91"/>
+    <mergeCell ref="B88:H88"/>
     <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B60:H60"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="A68:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="B92:H92"/>
+    <mergeCell ref="A70:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A66:A67"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="A38:A47"/>
     <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="A50:A57"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A18:A23"/>
     <mergeCell ref="A24:A25"/>
@@ -6787,7 +6902,7 @@
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="35" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6804,7 +6919,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -6812,7 +6927,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -6823,16 +6938,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7041,7 +7156,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="8">
         <v>0</v>
@@ -7058,7 +7173,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
@@ -7075,7 +7190,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -7092,7 +7207,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -7109,7 +7224,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>0</v>
@@ -7126,7 +7241,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
@@ -7143,7 +7258,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
@@ -7160,7 +7275,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
@@ -7177,7 +7292,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
@@ -7194,7 +7309,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B28" s="8">
         <v>0</v>
@@ -7211,7 +7326,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" s="8">
         <v>0</v>
@@ -7228,7 +7343,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" s="8">
         <v>0</v>
@@ -7245,7 +7360,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="8">
         <v>0</v>
@@ -7262,7 +7377,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B32" s="8">
         <v>0</v>
@@ -7279,7 +7394,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="8">
         <v>0</v>
@@ -7329,40 +7444,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>123</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>127</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -7543,13 +7658,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86DDF764-0B5A-44B5-AB40-319194553184}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59743377-9C10-4BFE-8B7D-335D11EE0CE1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35247376-8E7F-4853-B503-C64174BE633A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{500826EE-C1E2-4C90-A473-C9A273C1553E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2C474F2-04FB-4666-8D32-FACE7FBF4504}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77F59206-CB2D-4DC9-8065-5A34FCDCFC56}"/>
 </file>
--- a/Plannings 2026 S39.xlsx
+++ b/Plannings 2026 S39.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0320468-921D-4999-A3E8-1A9C3304F7BD}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B412682B-0820-4C1B-BF6E-123A7D5EFA93}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="135">
   <si>
     <t>Planning des salariés du 21/09/2026 au 27/09/2026</t>
   </si>
@@ -421,6 +421,12 @@
   </si>
   <si>
     <t>17:15/22:30</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF</t>
+  </si>
+  <si>
+    <t>P50 // P25 // EDF // C. PADEL</t>
   </si>
 </sst>
 </file>
@@ -5545,8 +5551,12 @@
       <c r="H3" s="58"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
+      <c r="B4" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>133</v>
+      </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
       <c r="F4" s="16"/>
@@ -7658,13 +7668,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59743377-9C10-4BFE-8B7D-335D11EE0CE1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49E86FFD-E0CC-4380-9F28-7E18E73614DF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{500826EE-C1E2-4C90-A473-C9A273C1553E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D994265-079E-4BB0-8F08-015B28DF3D96}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77F59206-CB2D-4DC9-8065-5A34FCDCFC56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BEE6FBF-1027-471A-8E84-B3804C65822A}"/>
 </file>
--- a/Plannings 2026 S39.xlsx
+++ b/Plannings 2026 S39.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B412682B-0820-4C1B-BF6E-123A7D5EFA93}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3A90C46-4542-46BF-902B-EDA33E03FAAE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="138">
   <si>
     <t>Planning des salariés du 21/09/2026 au 27/09/2026</t>
   </si>
@@ -427,6 +427,15 @@
   </si>
   <si>
     <t>P50 // P25 // EDF // C. PADEL</t>
+  </si>
+  <si>
+    <t>C. PADEL</t>
+  </si>
+  <si>
+    <t>EDF // C. PADEL // BUSINESS CUP</t>
+  </si>
+  <si>
+    <t>EDF // ANNIV // OPC</t>
   </si>
 </sst>
 </file>
@@ -5557,11 +5566,21 @@
       <c r="C4" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
+      <c r="D4" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
@@ -7668,13 +7687,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49E86FFD-E0CC-4380-9F28-7E18E73614DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE576DB-D324-41E4-BD12-3B22CCEA9DC5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D994265-079E-4BB0-8F08-015B28DF3D96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{286AD396-E83A-42B7-B89C-FFF5A03C7C6D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BEE6FBF-1027-471A-8E84-B3804C65822A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB3BAFC6-FBA3-4F86-BD6F-E62563498196}"/>
 </file>
--- a/Plannings 2026 S39.xlsx
+++ b/Plannings 2026 S39.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3A90C46-4542-46BF-902B-EDA33E03FAAE}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{38550F53-A7D0-45C7-9442-056190286F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E75F243B-FCB3-4DCA-A8DE-78B9BB6DD35D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,9 +63,6 @@
     <t>VDC</t>
   </si>
   <si>
-    <t>18:00/23:15</t>
-  </si>
-  <si>
     <t>20:00/22:30</t>
   </si>
   <si>
@@ -436,6 +433,9 @@
   </si>
   <si>
     <t>EDF // ANNIV // OPC</t>
+  </si>
+  <si>
+    <t>17:45/23:15</t>
   </si>
 </sst>
 </file>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="56" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C3" s="57"/>
       <c r="D3" s="57"/>
@@ -5561,25 +5561,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="D4" s="16" t="s">
+      <c r="F4" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>137</v>
-      </c>
       <c r="H4" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5627,11 +5627,11 @@
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="20"/>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -5643,7 +5643,7 @@
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -5655,7 +5655,7 @@
       <c r="B9" s="23"/>
       <c r="C9" s="24"/>
       <c r="D9" s="38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
@@ -5664,17 +5664,17 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" s="19"/>
     </row>
@@ -5683,18 +5683,18 @@
       <c r="B11" s="24"/>
       <c r="C11" s="24"/>
       <c r="D11" s="48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="28"/>
@@ -5706,7 +5706,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18" t="s">
@@ -5730,20 +5730,20 @@
       <c r="A14" s="20"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -5751,7 +5751,7 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -5763,7 +5763,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
       <c r="D16" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
@@ -5772,7 +5772,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="30"/>
       <c r="C17" s="31"/>
@@ -5784,7 +5784,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="18" t="s">
         <v>12</v>
@@ -5796,7 +5796,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" s="18"/>
       <c r="G18" s="18" t="s">
@@ -5807,33 +5807,33 @@
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
       <c r="B19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="41" t="s">
         <v>33</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="41" t="s">
-        <v>34</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="20"/>
       <c r="B20" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>12</v>
@@ -5845,16 +5845,16 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="20"/>
       <c r="B21" s="41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -5879,13 +5879,13 @@
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22"/>
       <c r="B23" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="D23" s="24" t="s">
         <v>38</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>39</v>
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
@@ -5894,7 +5894,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18" t="s">
@@ -5914,57 +5914,57 @@
       <c r="A25" s="22"/>
       <c r="B25" s="24"/>
       <c r="C25" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>41</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>42</v>
       </c>
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H25" s="25"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="36" t="s">
+      <c r="C26" s="45" t="s">
         <v>45</v>
-      </c>
-      <c r="C26" s="45" t="s">
-        <v>46</v>
       </c>
       <c r="D26" s="18" t="s">
         <v>12</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" s="36" t="s">
         <v>46</v>
-      </c>
-      <c r="G26" s="36" t="s">
-        <v>47</v>
       </c>
       <c r="H26" s="19"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="20"/>
       <c r="B27" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="D27" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="37" t="s">
         <v>51</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>52</v>
       </c>
       <c r="H27" s="21"/>
     </row>
@@ -5972,14 +5972,14 @@
       <c r="A28" s="20"/>
       <c r="B28" s="37"/>
       <c r="C28" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G28" s="37"/>
       <c r="H28" s="21"/>
@@ -5988,14 +5988,14 @@
       <c r="A29" s="20"/>
       <c r="B29" s="37"/>
       <c r="C29" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="46" t="s">
         <v>53</v>
-      </c>
-      <c r="D29" s="46" t="s">
-        <v>54</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G29" s="37"/>
       <c r="H29" s="21"/>
@@ -6004,12 +6004,12 @@
       <c r="A30" s="20"/>
       <c r="B30" s="37"/>
       <c r="C30" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" s="46"/>
       <c r="E30" s="2"/>
       <c r="F30" s="47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G30" s="37"/>
       <c r="H30" s="21"/>
@@ -6018,12 +6018,12 @@
       <c r="A31" s="20"/>
       <c r="B31" s="37"/>
       <c r="C31" s="44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D31" s="46"/>
       <c r="E31" s="2"/>
       <c r="F31" s="46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G31" s="37"/>
       <c r="H31" s="21"/>
@@ -6032,12 +6032,12 @@
       <c r="A32" s="20"/>
       <c r="B32" s="37"/>
       <c r="C32" s="47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" s="46"/>
       <c r="E32" s="2"/>
       <c r="F32" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G32" s="37"/>
       <c r="H32" s="21"/>
@@ -6046,19 +6046,19 @@
       <c r="A33" s="22"/>
       <c r="B33" s="38"/>
       <c r="C33" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D33" s="48"/>
       <c r="E33" s="24"/>
       <c r="F33" s="50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="25"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -6066,7 +6066,7 @@
       <c r="E34" s="18"/>
       <c r="F34" s="18"/>
       <c r="G34" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H34" s="19"/>
     </row>
@@ -6078,7 +6078,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H35" s="21"/>
     </row>
@@ -6090,7 +6090,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H36" s="21"/>
     </row>
@@ -6102,50 +6102,50 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H37" s="21"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" s="18"/>
       <c r="D38" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E38" s="18"/>
       <c r="F38" s="18" t="s">
         <v>12</v>
       </c>
       <c r="G38" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H38" s="55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="20"/>
       <c r="B39" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="G39" s="46" t="s">
+      <c r="H39" s="54" t="s">
         <v>66</v>
-      </c>
-      <c r="H39" s="54" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -6155,14 +6155,14 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G40" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H40" s="34" t="s">
         <v>12</v>
@@ -6171,21 +6171,21 @@
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="20"/>
       <c r="B41" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G41" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="H41" s="21" t="s">
         <v>71</v>
-      </c>
-      <c r="H41" s="21" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6193,7 +6193,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="46"/>
@@ -6205,7 +6205,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="46"/>
@@ -6217,7 +6217,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="46"/>
@@ -6229,7 +6229,7 @@
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="46"/>
@@ -6241,7 +6241,7 @@
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="46"/>
@@ -6253,7 +6253,7 @@
       <c r="B47" s="24"/>
       <c r="C47" s="24"/>
       <c r="D47" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E47" s="24"/>
       <c r="F47" s="48"/>
@@ -6262,7 +6262,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -6281,10 +6281,10 @@
       <c r="B49" s="24"/>
       <c r="C49" s="24"/>
       <c r="D49" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F49" s="24"/>
       <c r="G49" s="24"/>
@@ -6292,53 +6292,53 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C50" s="18"/>
       <c r="D50" s="45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E50" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F50" s="18"/>
       <c r="G50" s="36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H50" s="19"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="20"/>
       <c r="B51" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H51" s="21"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="20"/>
       <c r="B52" s="47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="37"/>
@@ -6347,14 +6347,14 @@
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="20"/>
       <c r="B53" s="46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="37"/>
@@ -6365,10 +6365,10 @@
       <c r="B54" s="46"/>
       <c r="C54" s="2"/>
       <c r="D54" s="47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E54" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="37"/>
@@ -6379,10 +6379,10 @@
       <c r="B55" s="46"/>
       <c r="C55" s="2"/>
       <c r="D55" s="46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="37"/>
@@ -6394,7 +6394,7 @@
       <c r="C56" s="2"/>
       <c r="D56" s="46"/>
       <c r="E56" s="47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="37"/>
@@ -6406,7 +6406,7 @@
       <c r="C57" s="24"/>
       <c r="D57" s="48"/>
       <c r="E57" s="48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F57" s="24"/>
       <c r="G57" s="38"/>
@@ -6414,17 +6414,17 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
       <c r="D58" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E58" s="18"/>
       <c r="F58" s="18"/>
       <c r="G58" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H58" s="19"/>
     </row>
@@ -6433,12 +6433,12 @@
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H59" s="21"/>
     </row>
@@ -6450,7 +6450,7 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H60" s="21"/>
     </row>
@@ -6462,13 +6462,13 @@
       <c r="E61" s="24"/>
       <c r="F61" s="24"/>
       <c r="G61" s="48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H61" s="25"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B62" s="30"/>
       <c r="C62" s="31"/>
@@ -6480,7 +6480,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
@@ -6501,12 +6501,12 @@
       <c r="F64" s="24"/>
       <c r="G64" s="24"/>
       <c r="H64" s="25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B65" s="30"/>
       <c r="C65" s="31"/>
@@ -6518,16 +6518,16 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
       <c r="D66" s="36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E66" s="18"/>
       <c r="F66" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G66" s="18"/>
       <c r="H66" s="19"/>
@@ -6537,18 +6537,18 @@
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="21"/>
     </row>
     <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B68" s="30"/>
       <c r="C68" s="31"/>
@@ -6560,7 +6560,7 @@
     </row>
     <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B69" s="30"/>
       <c r="C69" s="31"/>
@@ -6572,7 +6572,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B70" s="18"/>
       <c r="C70" s="18"/>
@@ -6580,7 +6580,7 @@
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
       <c r="G70" s="51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H70" s="19" t="s">
         <v>12</v>
@@ -6594,10 +6594,10 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="H71" s="21" t="s">
         <v>96</v>
-      </c>
-      <c r="H71" s="21" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -6611,7 +6611,7 @@
         <v>12</v>
       </c>
       <c r="H72" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -6622,10 +6622,10 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H73" s="54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -6649,7 +6649,7 @@
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -6661,7 +6661,7 @@
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6673,21 +6673,21 @@
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B78" s="18"/>
       <c r="C78" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D78" s="18"/>
       <c r="E78" s="18"/>
       <c r="F78" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G78" s="18"/>
       <c r="H78" s="19"/>
@@ -6696,22 +6696,22 @@
       <c r="A79" s="22"/>
       <c r="B79" s="24"/>
       <c r="C79" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D79" s="24"/>
       <c r="E79" s="24"/>
       <c r="F79" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G79" s="24"/>
       <c r="H79" s="25"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" s="36" t="s">
         <v>101</v>
-      </c>
-      <c r="B80" s="36" t="s">
-        <v>102</v>
       </c>
       <c r="C80" s="18" t="s">
         <v>12</v>
@@ -6724,27 +6724,27 @@
         <v>12</v>
       </c>
       <c r="G80" s="45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H80" s="19"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="20"/>
       <c r="B81" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G81" s="46" t="s">
         <v>107</v>
-      </c>
-      <c r="G81" s="46" t="s">
-        <v>108</v>
       </c>
       <c r="H81" s="21"/>
     </row>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
@@ -6767,32 +6767,32 @@
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="22"/>
       <c r="B83" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C83" s="24"/>
       <c r="D83" s="38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E83" s="24"/>
       <c r="F83" s="24"/>
       <c r="G83" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H83" s="25"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
       <c r="D84" s="36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
       <c r="G84" s="51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H84" s="19"/>
     </row>
@@ -6801,12 +6801,12 @@
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H85" s="21"/>
     </row>
@@ -6818,7 +6818,7 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H86" s="21"/>
     </row>
@@ -6830,13 +6830,13 @@
       <c r="E87" s="24"/>
       <c r="F87" s="24"/>
       <c r="G87" s="48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H87" s="25"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B88" s="30"/>
       <c r="C88" s="31"/>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
@@ -6868,17 +6868,17 @@
       <c r="C90" s="24"/>
       <c r="D90" s="24"/>
       <c r="E90" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G90" s="24"/>
       <c r="H90" s="25"/>
     </row>
     <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B91" s="30"/>
       <c r="C91" s="31"/>
@@ -6948,7 +6948,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -6967,16 +6967,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6998,7 +6998,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>0</v>
@@ -7015,7 +7015,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="8">
         <v>0</v>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
@@ -7049,7 +7049,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="8">
         <v>0</v>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="8">
         <v>0</v>
@@ -7083,7 +7083,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="8">
         <v>0</v>
@@ -7100,7 +7100,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="8">
         <v>0</v>
@@ -7117,7 +7117,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="8">
         <v>0</v>
@@ -7134,7 +7134,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" s="8">
         <v>0</v>
@@ -7151,7 +7151,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="8">
         <v>0</v>
@@ -7168,7 +7168,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="8">
         <v>0</v>
@@ -7202,7 +7202,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
@@ -7219,7 +7219,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -7236,7 +7236,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -7253,7 +7253,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="8">
         <v>0</v>
@@ -7270,7 +7270,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
@@ -7321,7 +7321,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B28" s="8">
         <v>0</v>
@@ -7355,7 +7355,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B29" s="8">
         <v>0</v>
@@ -7372,7 +7372,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="8">
         <v>0</v>
@@ -7389,7 +7389,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="8">
         <v>0</v>
@@ -7406,7 +7406,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B32" s="8">
         <v>0</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B33" s="8">
         <v>0</v>
@@ -7473,40 +7473,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -7687,13 +7687,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE576DB-D324-41E4-BD12-3B22CCEA9DC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A974BE8-991D-46DE-BF4B-9F77235EE340}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{286AD396-E83A-42B7-B89C-FFF5A03C7C6D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEE58ED-6DDD-4117-A935-C217135C53CB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB3BAFC6-FBA3-4F86-BD6F-E62563498196}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C750A7A4-87BA-4CA5-84B9-4BDEDAC75CC1}"/>
 </file>
--- a/Plannings 2026 S39.xlsx
+++ b/Plannings 2026 S39.xlsx
@@ -7687,13 +7687,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A974BE8-991D-46DE-BF4B-9F77235EE340}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C088225D-6612-421B-8F91-F3DBB4613A24}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEE58ED-6DDD-4117-A935-C217135C53CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD012133-47B6-4034-8DD6-54022428BF48}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C750A7A4-87BA-4CA5-84B9-4BDEDAC75CC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62E56161-25EE-474A-94C1-C9516A892293}"/>
 </file>
--- a/Plannings 2026 S39.xlsx
+++ b/Plannings 2026 S39.xlsx
@@ -7687,13 +7687,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C088225D-6612-421B-8F91-F3DBB4613A24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A974BE8-991D-46DE-BF4B-9F77235EE340}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD012133-47B6-4034-8DD6-54022428BF48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEE58ED-6DDD-4117-A935-C217135C53CB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62E56161-25EE-474A-94C1-C9516A892293}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C750A7A4-87BA-4CA5-84B9-4BDEDAC75CC1}"/>
 </file>